--- a/Financial_Sector_Projects/Investment_Allocation/Optimal_allocation_of_investments.xlsx
+++ b/Financial_Sector_Projects/Investment_Allocation/Optimal_allocation_of_investments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Financial_Sector_Projects\Investment_Allocation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09302093-7C19-49C9-8C9E-2FC589AD91D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16B1247-E84B-4CEA-84B0-D1EFACDF7536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{138FF08B-9763-4E07-B7F6-47B4B22FAA05}"/>
   </bookViews>

--- a/Financial_Sector_Projects/Investment_Allocation/Optimal_allocation_of_investments.xlsx
+++ b/Financial_Sector_Projects/Investment_Allocation/Optimal_allocation_of_investments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Financial_Sector_Projects\Investment_Allocation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16B1247-E84B-4CEA-84B0-D1EFACDF7536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49276E18-A000-48A5-B8AF-2F96F3925217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{138FF08B-9763-4E07-B7F6-47B4B22FAA05}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{138FF08B-9763-4E07-B7F6-47B4B22FAA05}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -249,17 +249,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -785,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E26A72D-2978-4EF0-BB59-104E1644A77C}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
@@ -853,10 +853,10 @@
       <c r="G4" s="5">
         <v>0.11799999999999999</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="9">
         <v>250000</v>
       </c>
     </row>
@@ -1021,54 +1021,6 @@
       <c r="J15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
